--- a/data/frise-philosophes-coreens.xlsx
+++ b/data/frise-philosophes-coreens.xlsx
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9.869999999999999" customWidth="1" style="23" min="1" max="1"/>
@@ -758,6 +758,11 @@
       <c r="M3" s="24" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="N3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traditions</t>
         </is>
       </c>
     </row>
